--- a/docs/package/05_Delivery/Upload_Templates/Remittance_Policy_List_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Remittance_Policy_List_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t xml:space="preserve">Policy No</t>
   </si>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Code of an active insurer (Allowed values). Must be the policy's insurer.</t>
   </si>
   <si>
-    <t xml:space="preserve">AXA, FPG, MAAGAP, MALAYAN, MAPFRE, MERCANTILE, PIONEER, STANDARD, STRONGHOLD</t>
+    <t xml:space="preserve">AXA, MAAGAP, MALAYAN, PIONEER, STANDARD, STRONGHOLD</t>
   </si>
   <si>
     <t xml:space="preserve">insurerCode, Insurer, Insurance Company</t>
@@ -138,12 +138,6 @@
     <t xml:space="preserve">Accounts &gt; Remittance &gt; Remittances &gt; Import policy list</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/remittance/imports/validate (multipart field "file" and field purposeCode, a reason of the remittance_off_cycle context; optional note)</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -174,10 +168,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -207,10 +201,10 @@
     <t xml:space="preserve">6. The drafts still need Submit for approval and approval by another user.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -613,7 +607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -709,44 +703,36 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="17">
       <c r="B17" s="4" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Remittance_Policy_List_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Remittance_Policy_List_Template.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Code of an active insurer (Allowed values). Must be the policy's insurer.</t>
   </si>
   <si>
-    <t xml:space="preserve">AXA, MAAGAP, MALAYAN, PIONEER, STANDARD, STRONGHOLD</t>
+    <t xml:space="preserve">AXA, CTINS, MAAGAP, MALAYAN, PIONEER, STANDARD, STRONGHOLD</t>
   </si>
   <si>
     <t xml:space="preserve">insurerCode, Insurer, Insurance Company</t>
